--- a/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
-    <sheet name="questionnaireCMS" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>

--- a/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
@@ -9,22 +9,37 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9045"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="QuestionnaireList (21)" type="4" refreshedVersion="0" background="1">
+    <webPr xml="1" sourceData="1" url="C:\Users\costco majors\Downloads\QuestionnaireList (21).xls" htmlTables="1" htmlFormat="all"/>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+  <si>
+    <t>questionnaireCMS</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
   <si>
     <t>ACCESS_CODE_TITLE</t>
   </si>
@@ -176,26 +191,102 @@
     <t>CONFIRMATION_PAGE_EXIT_LINK</t>
   </si>
   <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TEXT</t>
+    <t>CONTACT_US_EMAIL</t>
+  </si>
+  <si>
+    <t>ESIGNATURE_PAGE_TEXT</t>
+  </si>
+  <si>
+    <t>CONFIRMATION_PAGE_HEADLINE</t>
+  </si>
+  <si>
+    <t>CONFIRMATION_PAGE_SIGNOFF_STATEMENT</t>
+  </si>
+  <si>
+    <t>RETRIEVE_ACCESS_CODE_TEXT</t>
+  </si>
+  <si>
+    <t>SAVE_FOR_LATER_TEXT</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_PDF</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_FAQ</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_DOC_OTHER</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_VIDEO</t>
+  </si>
+  <si>
+    <t>CONFIRMATION_PAGE_SIGNOFF_INCOMPLETE_STATEMENT</t>
+  </si>
+  <si>
+    <t>WARNING</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_TITLE</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_PAGE_PN</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_PAGE_SITE</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_SUBTITLE</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_PANEL_ONE</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_PANEL_TWO</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_HEADER</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_HEADER_TEXT</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_PREVIOUS_TEXT</t>
+  </si>
+  <si>
+    <t>REDIRECT_PAGE_NEXT_TEXT</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_TITLE</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_SUBTITLE</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_PANEL_ONE</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_PANEL_TWO</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_HEADER</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_HEADER_TEXT</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_PREVIOUS_TEXT</t>
+  </si>
+  <si>
+    <t>REDIRECT_CONFIRMATION_PAGE_NEXT_TEXT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -225,7 +316,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -241,6 +332,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
+<MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
+  <Schema ID="Schema1">
+    <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
+      <xsd:element nillable="true" name="ArrayOfView_QuestionnaireCMS">
+        <xsd:complexType>
+          <xsd:sequence minOccurs="0">
+            <xsd:element minOccurs="0" maxOccurs="unbounded" nillable="true" name="view_QuestionnaireCMS" form="unqualified">
+              <xsd:complexType>
+                <xsd:sequence minOccurs="0">
+                  <xsd:element minOccurs="0" nillable="true" type="xsd:integer" name="questionnaireCMS" form="unqualified"/>
+                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="description" form="unqualified"/>
+                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="text" form="unqualified"/>
+                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="link" form="unqualified"/>
+                </xsd:sequence>
+              </xsd:complexType>
+            </xsd:element>
+          </xsd:sequence>
+        </xsd:complexType>
+      </xsd:element>
+    </xsd:schema>
+  </Schema>
+  <Map ID="1" Name="ArrayOfView_QuestionnaireCMS_Map" RootElement="ArrayOfView_QuestionnaireCMS" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
+    <DataBinding FileBinding="true" ConnectionID="1" DataBindingLoadMode="1"/>
+  </Map>
+</MapInfo>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D81" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:D81"/>
+  <tableColumns count="4">
+    <tableColumn id="1" uniqueName="questionnaireCMS" name="questionnaireCMS">
+      <xmlColumnPr mapId="1" xpath="/ArrayOfView_QuestionnaireCMS/view_QuestionnaireCMS/questionnaireCMS" xmlDataType="integer"/>
+    </tableColumn>
+    <tableColumn id="2" uniqueName="description" name="description">
+      <xmlColumnPr mapId="1" xpath="/ArrayOfView_QuestionnaireCMS/view_QuestionnaireCMS/description" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="3" uniqueName="text" name="text">
+      <xmlColumnPr mapId="1" xpath="/ArrayOfView_QuestionnaireCMS/view_QuestionnaireCMS/text" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="4" uniqueName="link" name="link">
+      <xmlColumnPr mapId="1" xpath="/ArrayOfView_QuestionnaireCMS/view_QuestionnaireCMS/link" xmlDataType="string"/>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,273 +646,833 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>49</v>
       </c>
+      <c r="B51" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>58</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>59</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>60</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>61</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>62</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>63</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>64</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>65</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>68</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>84</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>85</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>69</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>70</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>71</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>72</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>73</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>74</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>75</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>76</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>77</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>78</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>79</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>80</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>81</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>82</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>83</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
+++ b/UploadTemplates/addQuestionnaireCMSTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john\Desktop\hs3MVC_Latest\Generic\UploadTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\standard\genericlatest1\Generic\UploadTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>questionnaireCMS</t>
   </si>
@@ -279,6 +279,18 @@
   </si>
   <si>
     <t>REDIRECT_CONFIRMATION_PAGE_NEXT_TEXT</t>
+  </si>
+  <si>
+    <t>QUESTIONNAIRE_DOC_OTHER_2</t>
+  </si>
+  <si>
+    <t>SAVE_FOR_LATER_TEXT_NOTICE</t>
+  </si>
+  <si>
+    <t>SAVE_FOR_LATER_TEXT_PAGE_PREVIOUS_TEXT</t>
+  </si>
+  <si>
+    <t>SAVE_FOR_LATER_TEXT_PAGE_NEXT_TEXT</t>
   </si>
 </sst>
 </file>
@@ -363,8 +375,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D81" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:D81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D85" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:D85"/>
   <tableColumns count="4">
     <tableColumn id="1" uniqueName="questionnaireCMS" name="questionnaireCMS">
       <xmlColumnPr mapId="1" xpath="/ArrayOfView_QuestionnaireCMS/view_QuestionnaireCMS/questionnaireCMS" xmlDataType="integer"/>
@@ -646,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1469,10 +1481,43 @@
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
     </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>86</v>
+      </c>
+      <c r="B82" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>87</v>
+      </c>
+      <c r="B83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>88</v>
+      </c>
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>89</v>
+      </c>
+      <c r="B85" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>